--- a/RevitCadQC/docs/sample-output/QC_Issues.xlsx
+++ b/RevitCadQC/docs/sample-output/QC_Issues.xlsx
@@ -128,7 +128,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">/tmp/cadqc_test_f36f12f11ff549d595f4afdc0e473ee6</t>
+          <t xml:space="preserve">/tmp/cadqc_test_30b4df8eb6f1447fa9645dbda136e348</t>
         </is>
       </c>
     </row>
@@ -140,7 +140,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26 03:23</t>
+          <t xml:space="preserve">2026-09-26 05:08</t>
         </is>
       </c>
     </row>
@@ -151,7 +151,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7"/>

--- a/RevitCadQC/docs/sample-output/QC_Issues.xlsx
+++ b/RevitCadQC/docs/sample-output/QC_Issues.xlsx
@@ -128,7 +128,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">/tmp/cadqc_test_30b4df8eb6f1447fa9645dbda136e348</t>
+          <t xml:space="preserve">/tmp/cadqc_test_87e50d611c58425f99107f1094424321</t>
         </is>
       </c>
     </row>
@@ -140,7 +140,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-26 05:08</t>
+          <t xml:space="preserve">2026-09-26 05:23</t>
         </is>
       </c>
     </row>
@@ -151,7 +151,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7"/>
